--- a/Cronograma projeto grafico Gantt.xlsx
+++ b/Cronograma projeto grafico Gantt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32913533-B582-400E-A85A-C346FF5235E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A603F7-0A10-44A2-806A-828BFC40512F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -248,7 +248,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="d/m/yy;@"/>
     <numFmt numFmtId="167" formatCode="ddd\,\ dd/mm/yyyy"/>
-    <numFmt numFmtId="169" formatCode="d"/>
+    <numFmt numFmtId="168" formatCode="d"/>
   </numFmts>
   <fonts count="37" x14ac:knownFonts="1">
     <font>
@@ -1281,13 +1281,25 @@
     <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
@@ -1295,18 +1307,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
       <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="3" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -1365,7 +1365,7 @@
     <cellStyle name="Vírgula" xfId="4" builtinId="3" customBuiltin="1"/>
     <cellStyle name="zTextoOculto" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill>
@@ -1380,97 +1380,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF354867"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCDC800"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1582,15 +1492,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="ListaDeTarefasPendentes" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="20"/>
-      <tableStyleElement type="headerRow" dxfId="19"/>
-      <tableStyleElement type="totalRow" dxfId="18"/>
-      <tableStyleElement type="firstColumn" dxfId="17"/>
-      <tableStyleElement type="lastColumn" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="secondRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="12"/>
+      <tableStyleElement type="wholeTable" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="totalRow" dxfId="9"/>
+      <tableStyleElement type="firstColumn" dxfId="8"/>
+      <tableStyleElement type="lastColumn" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" dxfId="6"/>
+      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="4"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="3"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2049,106 +1959,106 @@
         <v>4</v>
       </c>
       <c r="B3" s="51"/>
-      <c r="C3" s="88" t="s">
+      <c r="C3" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="89"/>
-      <c r="E3" s="90">
+      <c r="D3" s="93"/>
+      <c r="E3" s="91">
         <v>46097</v>
       </c>
-      <c r="F3" s="90"/>
+      <c r="F3" s="91"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="88" t="s">
+      <c r="C4" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="89"/>
+      <c r="D4" s="93"/>
       <c r="E4" s="7">
-        <v>1</v>
-      </c>
-      <c r="I4" s="91">
+        <v>6</v>
+      </c>
+      <c r="I4" s="88">
         <f>I5</f>
-        <v>46097</v>
-      </c>
-      <c r="J4" s="92"/>
-      <c r="K4" s="92"/>
-      <c r="L4" s="92"/>
-      <c r="M4" s="92"/>
-      <c r="N4" s="92"/>
-      <c r="O4" s="93"/>
-      <c r="P4" s="91">
+        <v>46132</v>
+      </c>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="88">
         <f>P5</f>
-        <v>46104</v>
-      </c>
-      <c r="Q4" s="92"/>
-      <c r="R4" s="92"/>
-      <c r="S4" s="92"/>
-      <c r="T4" s="92"/>
-      <c r="U4" s="92"/>
-      <c r="V4" s="93"/>
-      <c r="W4" s="91">
+        <v>46139</v>
+      </c>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="90"/>
+      <c r="W4" s="88">
         <f>W5</f>
-        <v>46111</v>
-      </c>
-      <c r="X4" s="92"/>
-      <c r="Y4" s="92"/>
-      <c r="Z4" s="92"/>
-      <c r="AA4" s="92"/>
-      <c r="AB4" s="92"/>
-      <c r="AC4" s="93"/>
-      <c r="AD4" s="91">
+        <v>46146</v>
+      </c>
+      <c r="X4" s="89"/>
+      <c r="Y4" s="89"/>
+      <c r="Z4" s="89"/>
+      <c r="AA4" s="89"/>
+      <c r="AB4" s="89"/>
+      <c r="AC4" s="90"/>
+      <c r="AD4" s="88">
         <f>AD5</f>
-        <v>46118</v>
-      </c>
-      <c r="AE4" s="92"/>
-      <c r="AF4" s="92"/>
-      <c r="AG4" s="92"/>
-      <c r="AH4" s="92"/>
-      <c r="AI4" s="92"/>
-      <c r="AJ4" s="93"/>
-      <c r="AK4" s="91">
+        <v>46153</v>
+      </c>
+      <c r="AE4" s="89"/>
+      <c r="AF4" s="89"/>
+      <c r="AG4" s="89"/>
+      <c r="AH4" s="89"/>
+      <c r="AI4" s="89"/>
+      <c r="AJ4" s="90"/>
+      <c r="AK4" s="88">
         <f>AK5</f>
-        <v>46125</v>
-      </c>
-      <c r="AL4" s="92"/>
-      <c r="AM4" s="92"/>
-      <c r="AN4" s="92"/>
-      <c r="AO4" s="92"/>
-      <c r="AP4" s="92"/>
-      <c r="AQ4" s="93"/>
-      <c r="AR4" s="91">
+        <v>46160</v>
+      </c>
+      <c r="AL4" s="89"/>
+      <c r="AM4" s="89"/>
+      <c r="AN4" s="89"/>
+      <c r="AO4" s="89"/>
+      <c r="AP4" s="89"/>
+      <c r="AQ4" s="90"/>
+      <c r="AR4" s="88">
         <f>AR5</f>
-        <v>46132</v>
-      </c>
-      <c r="AS4" s="92"/>
-      <c r="AT4" s="92"/>
-      <c r="AU4" s="92"/>
-      <c r="AV4" s="92"/>
-      <c r="AW4" s="92"/>
-      <c r="AX4" s="93"/>
-      <c r="AY4" s="91">
+        <v>46167</v>
+      </c>
+      <c r="AS4" s="89"/>
+      <c r="AT4" s="89"/>
+      <c r="AU4" s="89"/>
+      <c r="AV4" s="89"/>
+      <c r="AW4" s="89"/>
+      <c r="AX4" s="90"/>
+      <c r="AY4" s="88">
         <f>AY5</f>
-        <v>46139</v>
-      </c>
-      <c r="AZ4" s="92"/>
-      <c r="BA4" s="92"/>
-      <c r="BB4" s="92"/>
-      <c r="BC4" s="92"/>
-      <c r="BD4" s="92"/>
-      <c r="BE4" s="93"/>
-      <c r="BF4" s="91">
+        <v>46174</v>
+      </c>
+      <c r="AZ4" s="89"/>
+      <c r="BA4" s="89"/>
+      <c r="BB4" s="89"/>
+      <c r="BC4" s="89"/>
+      <c r="BD4" s="89"/>
+      <c r="BE4" s="90"/>
+      <c r="BF4" s="88">
         <f>BF5</f>
-        <v>46146</v>
-      </c>
-      <c r="BG4" s="92"/>
-      <c r="BH4" s="92"/>
-      <c r="BI4" s="92"/>
-      <c r="BJ4" s="92"/>
-      <c r="BK4" s="92"/>
-      <c r="BL4" s="93"/>
+        <v>46181</v>
+      </c>
+      <c r="BG4" s="89"/>
+      <c r="BH4" s="89"/>
+      <c r="BI4" s="89"/>
+      <c r="BJ4" s="89"/>
+      <c r="BK4" s="89"/>
+      <c r="BL4" s="90"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="46" t="s">
@@ -2162,227 +2072,227 @@
       <c r="G5" s="66"/>
       <c r="I5" s="85">
         <f>Início_do_projeto-WEEKDAY(Início_do_projeto,1)+2+7*(Semana_de_exibição-1)</f>
-        <v>46097</v>
+        <v>46132</v>
       </c>
       <c r="J5" s="86">
         <f>I5+1</f>
-        <v>46098</v>
+        <v>46133</v>
       </c>
       <c r="K5" s="86">
         <f t="shared" ref="K5:AX5" si="0">J5+1</f>
-        <v>46099</v>
+        <v>46134</v>
       </c>
       <c r="L5" s="86">
         <f t="shared" si="0"/>
-        <v>46100</v>
+        <v>46135</v>
       </c>
       <c r="M5" s="86">
         <f t="shared" si="0"/>
-        <v>46101</v>
+        <v>46136</v>
       </c>
       <c r="N5" s="86">
         <f t="shared" si="0"/>
-        <v>46102</v>
+        <v>46137</v>
       </c>
       <c r="O5" s="87">
         <f t="shared" si="0"/>
-        <v>46103</v>
+        <v>46138</v>
       </c>
       <c r="P5" s="85">
         <f>O5+1</f>
-        <v>46104</v>
+        <v>46139</v>
       </c>
       <c r="Q5" s="86">
         <f>P5+1</f>
-        <v>46105</v>
+        <v>46140</v>
       </c>
       <c r="R5" s="86">
         <f t="shared" si="0"/>
-        <v>46106</v>
+        <v>46141</v>
       </c>
       <c r="S5" s="86">
         <f t="shared" si="0"/>
-        <v>46107</v>
+        <v>46142</v>
       </c>
       <c r="T5" s="86">
         <f t="shared" si="0"/>
-        <v>46108</v>
+        <v>46143</v>
       </c>
       <c r="U5" s="86">
         <f t="shared" si="0"/>
-        <v>46109</v>
+        <v>46144</v>
       </c>
       <c r="V5" s="87">
         <f t="shared" si="0"/>
-        <v>46110</v>
+        <v>46145</v>
       </c>
       <c r="W5" s="85">
         <f>V5+1</f>
-        <v>46111</v>
+        <v>46146</v>
       </c>
       <c r="X5" s="86">
         <f>W5+1</f>
-        <v>46112</v>
+        <v>46147</v>
       </c>
       <c r="Y5" s="86">
         <f t="shared" si="0"/>
-        <v>46113</v>
+        <v>46148</v>
       </c>
       <c r="Z5" s="86">
         <f t="shared" si="0"/>
-        <v>46114</v>
+        <v>46149</v>
       </c>
       <c r="AA5" s="86">
         <f t="shared" si="0"/>
-        <v>46115</v>
+        <v>46150</v>
       </c>
       <c r="AB5" s="86">
         <f t="shared" si="0"/>
-        <v>46116</v>
+        <v>46151</v>
       </c>
       <c r="AC5" s="87">
         <f t="shared" si="0"/>
-        <v>46117</v>
+        <v>46152</v>
       </c>
       <c r="AD5" s="85">
         <f>AC5+1</f>
-        <v>46118</v>
+        <v>46153</v>
       </c>
       <c r="AE5" s="86">
         <f>AD5+1</f>
-        <v>46119</v>
+        <v>46154</v>
       </c>
       <c r="AF5" s="86">
         <f t="shared" si="0"/>
-        <v>46120</v>
+        <v>46155</v>
       </c>
       <c r="AG5" s="86">
         <f t="shared" si="0"/>
-        <v>46121</v>
+        <v>46156</v>
       </c>
       <c r="AH5" s="86">
         <f t="shared" si="0"/>
-        <v>46122</v>
+        <v>46157</v>
       </c>
       <c r="AI5" s="86">
         <f t="shared" si="0"/>
-        <v>46123</v>
+        <v>46158</v>
       </c>
       <c r="AJ5" s="87">
         <f t="shared" si="0"/>
-        <v>46124</v>
+        <v>46159</v>
       </c>
       <c r="AK5" s="85">
         <f>AJ5+1</f>
-        <v>46125</v>
+        <v>46160</v>
       </c>
       <c r="AL5" s="86">
         <f>AK5+1</f>
-        <v>46126</v>
+        <v>46161</v>
       </c>
       <c r="AM5" s="86">
         <f t="shared" si="0"/>
-        <v>46127</v>
+        <v>46162</v>
       </c>
       <c r="AN5" s="86">
         <f t="shared" si="0"/>
-        <v>46128</v>
+        <v>46163</v>
       </c>
       <c r="AO5" s="86">
         <f t="shared" si="0"/>
-        <v>46129</v>
+        <v>46164</v>
       </c>
       <c r="AP5" s="86">
         <f t="shared" si="0"/>
-        <v>46130</v>
+        <v>46165</v>
       </c>
       <c r="AQ5" s="87">
         <f t="shared" si="0"/>
-        <v>46131</v>
+        <v>46166</v>
       </c>
       <c r="AR5" s="85">
         <f>AQ5+1</f>
-        <v>46132</v>
+        <v>46167</v>
       </c>
       <c r="AS5" s="86">
         <f>AR5+1</f>
-        <v>46133</v>
+        <v>46168</v>
       </c>
       <c r="AT5" s="86">
         <f t="shared" si="0"/>
-        <v>46134</v>
+        <v>46169</v>
       </c>
       <c r="AU5" s="86">
         <f t="shared" si="0"/>
-        <v>46135</v>
+        <v>46170</v>
       </c>
       <c r="AV5" s="86">
         <f t="shared" si="0"/>
-        <v>46136</v>
+        <v>46171</v>
       </c>
       <c r="AW5" s="86">
         <f t="shared" si="0"/>
-        <v>46137</v>
+        <v>46172</v>
       </c>
       <c r="AX5" s="87">
         <f t="shared" si="0"/>
-        <v>46138</v>
+        <v>46173</v>
       </c>
       <c r="AY5" s="85">
         <f>AX5+1</f>
-        <v>46139</v>
+        <v>46174</v>
       </c>
       <c r="AZ5" s="86">
         <f>AY5+1</f>
-        <v>46140</v>
+        <v>46175</v>
       </c>
       <c r="BA5" s="86">
         <f t="shared" ref="BA5:BE5" si="1">AZ5+1</f>
-        <v>46141</v>
+        <v>46176</v>
       </c>
       <c r="BB5" s="86">
         <f t="shared" si="1"/>
-        <v>46142</v>
+        <v>46177</v>
       </c>
       <c r="BC5" s="86">
         <f t="shared" si="1"/>
-        <v>46143</v>
+        <v>46178</v>
       </c>
       <c r="BD5" s="86">
         <f t="shared" si="1"/>
-        <v>46144</v>
+        <v>46179</v>
       </c>
       <c r="BE5" s="87">
         <f t="shared" si="1"/>
-        <v>46145</v>
+        <v>46180</v>
       </c>
       <c r="BF5" s="85">
         <f>BE5+1</f>
-        <v>46146</v>
+        <v>46181</v>
       </c>
       <c r="BG5" s="86">
         <f>BF5+1</f>
-        <v>46147</v>
+        <v>46182</v>
       </c>
       <c r="BH5" s="86">
         <f t="shared" ref="BH5:BL5" si="2">BG5+1</f>
-        <v>46148</v>
+        <v>46183</v>
       </c>
       <c r="BI5" s="86">
         <f t="shared" si="2"/>
-        <v>46149</v>
+        <v>46184</v>
       </c>
       <c r="BJ5" s="86">
         <f t="shared" si="2"/>
-        <v>46150</v>
+        <v>46185</v>
       </c>
       <c r="BK5" s="86">
         <f t="shared" si="2"/>
-        <v>46151</v>
+        <v>46186</v>
       </c>
       <c r="BL5" s="87">
         <f t="shared" si="2"/>
-        <v>46152</v>
+        <v>46187</v>
       </c>
     </row>
     <row r="6" spans="1:64" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2789,13 +2699,13 @@
         <v>46097</v>
       </c>
       <c r="F9" s="72">
-        <f>E9+13</f>
-        <v>46110</v>
+        <f>E9+20</f>
+        <v>46117</v>
       </c>
       <c r="G9" s="14"/>
       <c r="H9" s="14">
         <f t="shared" si="6"/>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I9" s="31"/>
       <c r="J9" s="31"/>
@@ -2867,16 +2777,16 @@
       </c>
       <c r="E10" s="72">
         <f>F9+1</f>
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="F10" s="72">
-        <f>E10+6</f>
-        <v>46117</v>
+        <f>E10+15</f>
+        <v>46133</v>
       </c>
       <c r="G10" s="14"/>
       <c r="H10" s="14">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I10" s="31"/>
       <c r="J10" s="31"/>
@@ -3228,20 +3138,20 @@
       </c>
       <c r="C15" s="55"/>
       <c r="D15" s="20">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="75">
         <f>F10+1</f>
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="F15" s="75">
-        <f>E15+6</f>
-        <v>46124</v>
+        <f>E15+10</f>
+        <v>46144</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="14">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
@@ -3307,15 +3217,15 @@
       </c>
       <c r="C16" s="55"/>
       <c r="D16" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="75">
         <f>F15+1</f>
-        <v>46125</v>
+        <v>46145</v>
       </c>
       <c r="F16" s="75">
         <f>E16+13</f>
-        <v>46138</v>
+        <v>46158</v>
       </c>
       <c r="G16" s="14"/>
       <c r="H16" s="14">
@@ -3386,20 +3296,20 @@
       </c>
       <c r="C17" s="55"/>
       <c r="D17" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="75">
         <f>F16+1</f>
-        <v>46139</v>
+        <v>46159</v>
       </c>
       <c r="F17" s="75">
-        <f>E17+6</f>
-        <v>46145</v>
+        <f>E17+15</f>
+        <v>46174</v>
       </c>
       <c r="G17" s="14"/>
       <c r="H17" s="14">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
@@ -3680,20 +3590,20 @@
       </c>
       <c r="C21" s="57"/>
       <c r="D21" s="23">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E21" s="78">
         <f>F17+1</f>
-        <v>46146</v>
+        <v>46175</v>
       </c>
       <c r="F21" s="78">
-        <f>E21+6</f>
-        <v>46152</v>
+        <f>E21+10</f>
+        <v>46185</v>
       </c>
       <c r="G21" s="14"/>
       <c r="H21" s="14">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I21" s="31"/>
       <c r="J21" s="31"/>
@@ -4612,17 +4522,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D33">
     <cfRule type="dataBar" priority="14">
@@ -4639,15 +4549,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:BL33">
-    <cfRule type="expression" dxfId="5" priority="33">
+    <cfRule type="expression" dxfId="2" priority="33">
       <formula>AND(TODAY()&gt;=I$5,TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:BL33">
-    <cfRule type="expression" dxfId="3" priority="27">
+    <cfRule type="expression" dxfId="1" priority="27">
       <formula>AND(início_da_tarefa&lt;=I$5,ROUNDDOWN((término_da_tarefa-início_da_tarefa+1)*progresso_da_tarefa,0)+início_da_tarefa-1&gt;=I$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="28" stopIfTrue="1">
       <formula>AND(término_da_tarefa&gt;=I$5,início_da_tarefa&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4790,35 +4700,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5106,27 +4987,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{708DBB9E-6D89-4A94-9DC5-964B7833E11C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5145,4 +5035,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Cronograma projeto grafico Gantt.xlsx
+++ b/Cronograma projeto grafico Gantt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A603F7-0A10-44A2-806A-828BFC40512F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC50659E-B551-4A45-8973-2C2887ACE5A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1290,6 +1290,12 @@
     <xf numFmtId="168" fontId="11" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1301,12 +1307,6 @@
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -1959,106 +1959,106 @@
         <v>4</v>
       </c>
       <c r="B3" s="51"/>
-      <c r="C3" s="92" t="s">
+      <c r="C3" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="93"/>
-      <c r="E3" s="91">
+      <c r="D3" s="89"/>
+      <c r="E3" s="93">
         <v>46097</v>
       </c>
-      <c r="F3" s="91"/>
+      <c r="F3" s="93"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="92" t="s">
+      <c r="C4" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="93"/>
+      <c r="D4" s="89"/>
       <c r="E4" s="7">
         <v>6</v>
       </c>
-      <c r="I4" s="88">
+      <c r="I4" s="90">
         <f>I5</f>
         <v>46132</v>
       </c>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="90"/>
-      <c r="P4" s="88">
+      <c r="J4" s="91"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="91"/>
+      <c r="N4" s="91"/>
+      <c r="O4" s="92"/>
+      <c r="P4" s="90">
         <f>P5</f>
         <v>46139</v>
       </c>
-      <c r="Q4" s="89"/>
-      <c r="R4" s="89"/>
-      <c r="S4" s="89"/>
-      <c r="T4" s="89"/>
-      <c r="U4" s="89"/>
-      <c r="V4" s="90"/>
-      <c r="W4" s="88">
+      <c r="Q4" s="91"/>
+      <c r="R4" s="91"/>
+      <c r="S4" s="91"/>
+      <c r="T4" s="91"/>
+      <c r="U4" s="91"/>
+      <c r="V4" s="92"/>
+      <c r="W4" s="90">
         <f>W5</f>
         <v>46146</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="89"/>
-      <c r="Z4" s="89"/>
-      <c r="AA4" s="89"/>
-      <c r="AB4" s="89"/>
-      <c r="AC4" s="90"/>
-      <c r="AD4" s="88">
+      <c r="X4" s="91"/>
+      <c r="Y4" s="91"/>
+      <c r="Z4" s="91"/>
+      <c r="AA4" s="91"/>
+      <c r="AB4" s="91"/>
+      <c r="AC4" s="92"/>
+      <c r="AD4" s="90">
         <f>AD5</f>
         <v>46153</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="90"/>
-      <c r="AK4" s="88">
+      <c r="AE4" s="91"/>
+      <c r="AF4" s="91"/>
+      <c r="AG4" s="91"/>
+      <c r="AH4" s="91"/>
+      <c r="AI4" s="91"/>
+      <c r="AJ4" s="92"/>
+      <c r="AK4" s="90">
         <f>AK5</f>
         <v>46160</v>
       </c>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="89"/>
-      <c r="AQ4" s="90"/>
-      <c r="AR4" s="88">
+      <c r="AL4" s="91"/>
+      <c r="AM4" s="91"/>
+      <c r="AN4" s="91"/>
+      <c r="AO4" s="91"/>
+      <c r="AP4" s="91"/>
+      <c r="AQ4" s="92"/>
+      <c r="AR4" s="90">
         <f>AR5</f>
         <v>46167</v>
       </c>
-      <c r="AS4" s="89"/>
-      <c r="AT4" s="89"/>
-      <c r="AU4" s="89"/>
-      <c r="AV4" s="89"/>
-      <c r="AW4" s="89"/>
-      <c r="AX4" s="90"/>
-      <c r="AY4" s="88">
+      <c r="AS4" s="91"/>
+      <c r="AT4" s="91"/>
+      <c r="AU4" s="91"/>
+      <c r="AV4" s="91"/>
+      <c r="AW4" s="91"/>
+      <c r="AX4" s="92"/>
+      <c r="AY4" s="90">
         <f>AY5</f>
         <v>46174</v>
       </c>
-      <c r="AZ4" s="89"/>
-      <c r="BA4" s="89"/>
-      <c r="BB4" s="89"/>
-      <c r="BC4" s="89"/>
-      <c r="BD4" s="89"/>
-      <c r="BE4" s="90"/>
-      <c r="BF4" s="88">
+      <c r="AZ4" s="91"/>
+      <c r="BA4" s="91"/>
+      <c r="BB4" s="91"/>
+      <c r="BC4" s="91"/>
+      <c r="BD4" s="91"/>
+      <c r="BE4" s="92"/>
+      <c r="BF4" s="90">
         <f>BF5</f>
         <v>46181</v>
       </c>
-      <c r="BG4" s="89"/>
-      <c r="BH4" s="89"/>
-      <c r="BI4" s="89"/>
-      <c r="BJ4" s="89"/>
-      <c r="BK4" s="89"/>
-      <c r="BL4" s="90"/>
+      <c r="BG4" s="91"/>
+      <c r="BH4" s="91"/>
+      <c r="BI4" s="91"/>
+      <c r="BJ4" s="91"/>
+      <c r="BK4" s="91"/>
+      <c r="BL4" s="92"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="46" t="s">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C21" s="57"/>
       <c r="D21" s="23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E21" s="78">
         <f>F17+1</f>
@@ -4522,17 +4522,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D33">
     <cfRule type="dataBar" priority="14">
@@ -4700,6 +4700,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4987,15 +4996,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5017,6 +5017,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{708DBB9E-6D89-4A94-9DC5-964B7833E11C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5037,14 +5045,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
   <ds:schemaRefs>
